--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/169.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/169.xlsx
@@ -426,13 +426,13 @@
         <v>-7.777921863298209</v>
       </c>
       <c r="E2">
-        <v>-8.746532255770529</v>
+        <v>-9.645837380479778</v>
       </c>
       <c r="F2">
-        <v>-3.996378789903314</v>
+        <v>-3.838899824789761</v>
       </c>
       <c r="G2">
-        <v>-14.19278990662711</v>
+        <v>-15.17851477258172</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.772162670085148</v>
       </c>
       <c r="E3">
-        <v>-9.405601834372865</v>
+        <v>-10.78415989178788</v>
       </c>
       <c r="F3">
-        <v>-3.778373752113497</v>
+        <v>-3.716499945703193</v>
       </c>
       <c r="G3">
-        <v>-14.36447479829371</v>
+        <v>-14.4277658079135</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.80154011645697</v>
       </c>
       <c r="E4">
-        <v>-8.990458508193694</v>
+        <v>-11.90580403332572</v>
       </c>
       <c r="F4">
-        <v>-3.920734660558264</v>
+        <v>-4.140838108686038</v>
       </c>
       <c r="G4">
-        <v>-13.99920244567268</v>
+        <v>-14.40864906269698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.847011567293452</v>
       </c>
       <c r="E5">
-        <v>-10.33274348880726</v>
+        <v>-11.88275862910069</v>
       </c>
       <c r="F5">
-        <v>-3.838110347390915</v>
+        <v>-3.877275394679732</v>
       </c>
       <c r="G5">
-        <v>-13.62088654362693</v>
+        <v>-14.26729869980671</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.885668269767498</v>
       </c>
       <c r="E6">
-        <v>-11.15314901088087</v>
+        <v>-12.20226058423786</v>
       </c>
       <c r="F6">
-        <v>-3.965933627384906</v>
+        <v>-3.890709180107447</v>
       </c>
       <c r="G6">
-        <v>-13.69002728721461</v>
+        <v>-13.98739704027964</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.890597696443511</v>
       </c>
       <c r="E7">
-        <v>-11.62232156044556</v>
+        <v>-12.93806968337418</v>
       </c>
       <c r="F7">
-        <v>-3.758263062546289</v>
+        <v>-3.558841229968238</v>
       </c>
       <c r="G7">
-        <v>-12.87203121100717</v>
+        <v>-14.26514187938788</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.838721970460637</v>
       </c>
       <c r="E8">
-        <v>-12.44993188466537</v>
+        <v>-13.41372247924384</v>
       </c>
       <c r="F8">
-        <v>-3.699218546753917</v>
+        <v>-3.513636720170892</v>
       </c>
       <c r="G8">
-        <v>-12.92588716584003</v>
+        <v>-14.15306667070139</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.711744714602717</v>
       </c>
       <c r="E9">
-        <v>-12.8997044515812</v>
+        <v>-13.8871246235317</v>
       </c>
       <c r="F9">
-        <v>-3.594785019425052</v>
+        <v>-3.626018075636391</v>
       </c>
       <c r="G9">
-        <v>-12.19066134920545</v>
+        <v>-13.52992764966269</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.497738743368878</v>
       </c>
       <c r="E10">
-        <v>-13.93160782370904</v>
+        <v>-14.60842902042145</v>
       </c>
       <c r="F10">
-        <v>-3.813857475001875</v>
+        <v>-3.619395017498023</v>
       </c>
       <c r="G10">
-        <v>-11.91944490590066</v>
+        <v>-12.95585753460706</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.199254314868191</v>
       </c>
       <c r="E11">
-        <v>-14.99860234092233</v>
+        <v>-15.89458356570994</v>
       </c>
       <c r="F11">
-        <v>-3.675883431942875</v>
+        <v>-3.759518941337232</v>
       </c>
       <c r="G11">
-        <v>-11.46274852766712</v>
+        <v>-12.32276204785899</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.82837083028099</v>
       </c>
       <c r="E12">
-        <v>-14.89874496057918</v>
+        <v>-15.9264368518799</v>
       </c>
       <c r="F12">
-        <v>-3.842797325047658</v>
+        <v>-3.747336283582714</v>
       </c>
       <c r="G12">
-        <v>-11.58207052053907</v>
+        <v>-11.727691487175</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.408661352906916</v>
       </c>
       <c r="E13">
-        <v>-15.73419407330627</v>
+        <v>-16.68140592454267</v>
       </c>
       <c r="F13">
-        <v>-3.637979014562747</v>
+        <v>-3.604111463561074</v>
       </c>
       <c r="G13">
-        <v>-9.802364275718894</v>
+        <v>-11.25912018209209</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.978989778962091</v>
       </c>
       <c r="E14">
-        <v>-17.04298193168511</v>
+        <v>-18.05420376301992</v>
       </c>
       <c r="F14">
-        <v>-3.383332564860365</v>
+        <v>-3.917724035613014</v>
       </c>
       <c r="G14">
-        <v>-9.887955120091211</v>
+        <v>-10.75458973136162</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.580449431025209</v>
       </c>
       <c r="E15">
-        <v>-16.34218246510209</v>
+        <v>-18.44890555752847</v>
       </c>
       <c r="F15">
-        <v>-3.389731528611698</v>
+        <v>-3.454653968909223</v>
       </c>
       <c r="G15">
-        <v>-9.643160140735343</v>
+        <v>-10.88545228598347</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.260797074223661</v>
       </c>
       <c r="E16">
-        <v>-17.56389229678743</v>
+        <v>-18.40809494977134</v>
       </c>
       <c r="F16">
-        <v>-2.954206858895146</v>
+        <v>-2.957404361138419</v>
       </c>
       <c r="G16">
-        <v>-9.083830229693319</v>
+        <v>-9.568500717733698</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.065449984984823</v>
       </c>
       <c r="E17">
-        <v>-19.6882628524217</v>
+        <v>-20.27328735252462</v>
       </c>
       <c r="F17">
-        <v>-2.539254529020153</v>
+        <v>-2.977051816725361</v>
       </c>
       <c r="G17">
-        <v>-9.139804933671316</v>
+        <v>-10.55465264406288</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.022521451737433</v>
       </c>
       <c r="E18">
-        <v>-19.67356795426681</v>
+        <v>-21.28538317934291</v>
       </c>
       <c r="F18">
-        <v>-2.603104008559967</v>
+        <v>-2.605069387601028</v>
       </c>
       <c r="G18">
-        <v>-8.551818940441361</v>
+        <v>-9.692639554365289</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.138668900685185</v>
       </c>
       <c r="E19">
-        <v>-20.31675617452425</v>
+        <v>-21.42931619720271</v>
       </c>
       <c r="F19">
-        <v>-2.364460907133101</v>
+        <v>-2.46924047420449</v>
       </c>
       <c r="G19">
-        <v>-8.470869480915102</v>
+        <v>-9.141682012992083</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.395518946287265</v>
       </c>
       <c r="E20">
-        <v>-21.65014270371275</v>
+        <v>-21.15865383423826</v>
       </c>
       <c r="F20">
-        <v>-1.723725959717567</v>
+        <v>-1.940388806744049</v>
       </c>
       <c r="G20">
-        <v>-8.516591425357976</v>
+        <v>-9.93915270685604</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.759594882285552</v>
       </c>
       <c r="E21">
-        <v>-22.68123095051921</v>
+        <v>-23.37166926857268</v>
       </c>
       <c r="F21">
-        <v>-1.804680254997085</v>
+        <v>-1.813659075684669</v>
       </c>
       <c r="G21">
-        <v>-8.689991179613923</v>
+        <v>-9.834251450353154</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.193105316162881</v>
       </c>
       <c r="E22">
-        <v>-22.46577521418227</v>
+        <v>-23.72241316588877</v>
       </c>
       <c r="F22">
-        <v>-1.117740687498605</v>
+        <v>-1.715094762478422</v>
       </c>
       <c r="G22">
-        <v>-8.781742949234824</v>
+        <v>-9.681006297340291</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.65482377521768</v>
       </c>
       <c r="E23">
-        <v>-22.42851040157315</v>
+        <v>-24.81061905535398</v>
       </c>
       <c r="F23">
-        <v>-1.253477745952047</v>
+        <v>-1.405029691677067</v>
       </c>
       <c r="G23">
-        <v>-9.841756457090682</v>
+        <v>-9.709506783887877</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.1132790318228</v>
       </c>
       <c r="E24">
-        <v>-22.7606332137697</v>
+        <v>-24.25333598702205</v>
       </c>
       <c r="F24">
-        <v>-1.310241725226186</v>
+        <v>-0.9286549115776703</v>
       </c>
       <c r="G24">
-        <v>-8.951693115038848</v>
+        <v>-10.99104875704961</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.542585833324373</v>
       </c>
       <c r="E25">
-        <v>-22.84479943167626</v>
+        <v>-24.1041771101574</v>
       </c>
       <c r="F25">
-        <v>-0.7110632210317829</v>
+        <v>-1.340900688043178</v>
       </c>
       <c r="G25">
-        <v>-9.711526216666833</v>
+        <v>-10.49250377265414</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.919205066641729</v>
       </c>
       <c r="E26">
-        <v>-23.87702432545865</v>
+        <v>-23.91153582587111</v>
       </c>
       <c r="F26">
-        <v>-0.6805040316874632</v>
+        <v>-1.317635256292415</v>
       </c>
       <c r="G26">
-        <v>-10.41623542452041</v>
+        <v>-10.93992731283218</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.226834446883641</v>
       </c>
       <c r="E27">
-        <v>-22.20344071491792</v>
+        <v>-23.75685673919111</v>
       </c>
       <c r="F27">
-        <v>-0.7858283935937637</v>
+        <v>-0.910712315408699</v>
       </c>
       <c r="G27">
-        <v>-9.835403520200821</v>
+        <v>-11.0886502606384</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.452018832986797</v>
       </c>
       <c r="E28">
-        <v>-22.30478343473558</v>
+        <v>-24.49859813927748</v>
       </c>
       <c r="F28">
-        <v>-0.7749435828369484</v>
+        <v>-1.043129134410422</v>
       </c>
       <c r="G28">
-        <v>-10.25308180870851</v>
+        <v>-10.87347473222239</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.585132952979846</v>
       </c>
       <c r="E29">
-        <v>-23.11561576275697</v>
+        <v>-24.18545869012108</v>
       </c>
       <c r="F29">
-        <v>-0.2786434067624498</v>
+        <v>-0.7063295240505343</v>
       </c>
       <c r="G29">
-        <v>-10.659868402392</v>
+        <v>-11.62955367520884</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.620409709517444</v>
       </c>
       <c r="E30">
-        <v>-22.81884221866429</v>
+        <v>-22.96782448504264</v>
       </c>
       <c r="F30">
-        <v>-0.496749801730855</v>
+        <v>-0.9189998484641937</v>
       </c>
       <c r="G30">
-        <v>-10.54603860456969</v>
+        <v>-10.94648219299994</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.553689800468307</v>
       </c>
       <c r="E31">
-        <v>-22.2073804873046</v>
+        <v>-23.75406719920239</v>
       </c>
       <c r="F31">
-        <v>-0.6608074812171428</v>
+        <v>-0.6915915568014548</v>
       </c>
       <c r="G31">
-        <v>-10.6443154594485</v>
+        <v>-11.25466087725069</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.383075967013568</v>
       </c>
       <c r="E32">
-        <v>-22.49073616291255</v>
+        <v>-23.02348395907092</v>
       </c>
       <c r="F32">
-        <v>-0.4478275422970151</v>
+        <v>-0.7979033593460317</v>
       </c>
       <c r="G32">
-        <v>-9.998166491639088</v>
+        <v>-11.04874163416249</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.112463908777279</v>
       </c>
       <c r="E33">
-        <v>-21.23659340038427</v>
+        <v>-23.28612639456778</v>
       </c>
       <c r="F33">
-        <v>-0.2082983574104604</v>
+        <v>-0.8442140877253121</v>
       </c>
       <c r="G33">
-        <v>-9.590880005579173</v>
+        <v>-10.54409531433814</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.748027528762178</v>
       </c>
       <c r="E34">
-        <v>-22.41985195927048</v>
+        <v>-22.12683704860417</v>
       </c>
       <c r="F34">
-        <v>-0.4013853663267533</v>
+        <v>-0.6013456589160534</v>
       </c>
       <c r="G34">
-        <v>-10.36255823914667</v>
+        <v>-10.31919340312776</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.298801260332045</v>
       </c>
       <c r="E35">
-        <v>-21.55985851742182</v>
+        <v>-20.79827787270785</v>
       </c>
       <c r="F35">
-        <v>-0.6498941637538496</v>
+        <v>-0.7721356722488742</v>
       </c>
       <c r="G35">
-        <v>-9.270346365375858</v>
+        <v>-11.00606539161574</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.782274879523433</v>
       </c>
       <c r="E36">
-        <v>-20.86074817164366</v>
+        <v>-22.33412341783128</v>
       </c>
       <c r="F36">
-        <v>-0.8247931020842781</v>
+        <v>-0.336241207201067</v>
       </c>
       <c r="G36">
-        <v>-9.636644987114057</v>
+        <v>-9.969308466173262</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.215926591707793</v>
       </c>
       <c r="E37">
-        <v>-20.70233762238135</v>
+        <v>-20.52725776029679</v>
       </c>
       <c r="F37">
-        <v>-0.3118545116621727</v>
+        <v>-0.640665909384584</v>
       </c>
       <c r="G37">
-        <v>-9.006005925156131</v>
+        <v>-10.3939455214045</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.619016381010438</v>
       </c>
       <c r="E38">
-        <v>-19.58380907096078</v>
+        <v>-20.28340396345775</v>
       </c>
       <c r="F38">
-        <v>-0.4378026838522834</v>
+        <v>-1.02652714529887</v>
       </c>
       <c r="G38">
-        <v>-8.742579195505245</v>
+        <v>-10.22083378461047</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.015328419944092</v>
       </c>
       <c r="E39">
-        <v>-19.21324404291311</v>
+        <v>-20.26964645942245</v>
       </c>
       <c r="F39">
-        <v>-0.3528930830489551</v>
+        <v>-0.5635584357736682</v>
       </c>
       <c r="G39">
-        <v>-8.565395487697911</v>
+        <v>-8.983868307135026</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.423763473002113</v>
       </c>
       <c r="E40">
-        <v>-19.68905533537304</v>
+        <v>-19.15074657313325</v>
       </c>
       <c r="F40">
-        <v>-0.7316878231685507</v>
+        <v>-0.6300519123393088</v>
       </c>
       <c r="G40">
-        <v>-8.832410848713369</v>
+        <v>-10.27077005352483</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.865429082970559</v>
       </c>
       <c r="E41">
-        <v>-18.3626109568383</v>
+        <v>-20.08792785444265</v>
       </c>
       <c r="F41">
-        <v>-0.6090408859591736</v>
+        <v>-0.695246750054289</v>
       </c>
       <c r="G41">
-        <v>-8.382643442293524</v>
+        <v>-9.630831669147097</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.359273329239374</v>
       </c>
       <c r="E42">
-        <v>-19.48521513486578</v>
+        <v>-18.92364360164859</v>
       </c>
       <c r="F42">
-        <v>-0.8181700439459104</v>
+        <v>-0.9486682032310786</v>
       </c>
       <c r="G42">
-        <v>-7.766822382169376</v>
+        <v>-10.10956303849003</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.915336484457942</v>
       </c>
       <c r="E43">
-        <v>-18.09375092652891</v>
+        <v>-18.34235509260199</v>
       </c>
       <c r="F43">
-        <v>-0.5058561107446319</v>
+        <v>-0.8665134588676572</v>
       </c>
       <c r="G43">
-        <v>-7.869085133877464</v>
+        <v>-8.695738286670098</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.546238093250504</v>
       </c>
       <c r="E44">
-        <v>-17.85528601375899</v>
+        <v>-17.13155888327514</v>
       </c>
       <c r="F44">
-        <v>-0.8197901750974049</v>
+        <v>-1.206340323084907</v>
       </c>
       <c r="G44">
-        <v>-8.301127879480051</v>
+        <v>-9.112006282778056</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.255194127330269</v>
       </c>
       <c r="E45">
-        <v>-17.4286177212303</v>
+        <v>-17.44708936670759</v>
       </c>
       <c r="F45">
-        <v>-0.9835556608422942</v>
+        <v>-0.6699169576427505</v>
       </c>
       <c r="G45">
-        <v>-7.911946766974408</v>
+        <v>-9.438608152954854</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.040731700410469</v>
       </c>
       <c r="E46">
-        <v>-16.0602215594885</v>
+        <v>-16.75001230575887</v>
       </c>
       <c r="F46">
-        <v>-0.7170710094220024</v>
+        <v>-0.8383488328674821</v>
       </c>
       <c r="G46">
-        <v>-8.38747352823532</v>
+        <v>-9.071279951553942</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.902552963021865</v>
       </c>
       <c r="E47">
-        <v>-16.99083202501278</v>
+        <v>-15.95736632935228</v>
       </c>
       <c r="F47">
-        <v>-0.8651007931910852</v>
+        <v>-1.013514625644662</v>
       </c>
       <c r="G47">
-        <v>-7.705226371865697</v>
+        <v>-8.412792580519667</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.835460443863026</v>
       </c>
       <c r="E48">
-        <v>-14.90942763076328</v>
+        <v>-15.72333026416187</v>
       </c>
       <c r="F48">
-        <v>-1.234443184554381</v>
+        <v>-0.9289083045241406</v>
       </c>
       <c r="G48">
-        <v>-7.750587466844791</v>
+        <v>-8.924927354353841</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.83531672156855</v>
       </c>
       <c r="E49">
-        <v>-15.19611626324087</v>
+        <v>-16.76792242045921</v>
       </c>
       <c r="F49">
-        <v>-1.156333225098992</v>
+        <v>-1.519067603530116</v>
       </c>
       <c r="G49">
-        <v>-8.12424543131679</v>
+        <v>-10.59203863483787</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.896610781158822</v>
       </c>
       <c r="E50">
-        <v>-14.67227144698158</v>
+        <v>-15.54216413301101</v>
       </c>
       <c r="F50">
-        <v>-1.07899848968921</v>
+        <v>-1.340933154014444</v>
       </c>
       <c r="G50">
-        <v>-7.940841208441166</v>
+        <v>-9.519991293946758</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.013397892621538</v>
       </c>
       <c r="E51">
-        <v>-14.3951514800822</v>
+        <v>-16.75325016467436</v>
       </c>
       <c r="F51">
-        <v>-0.9493452375099289</v>
+        <v>-1.739703176845478</v>
       </c>
       <c r="G51">
-        <v>-8.623575015005065</v>
+        <v>-8.715035456618509</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.182698467715687</v>
       </c>
       <c r="E52">
-        <v>-13.84226556001171</v>
+        <v>-15.61829683802797</v>
       </c>
       <c r="F52">
-        <v>-1.573237472514764</v>
+        <v>-1.516292158913308</v>
       </c>
       <c r="G52">
-        <v>-8.336070687647057</v>
+        <v>-9.569424359939156</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.399158862163449</v>
       </c>
       <c r="E53">
-        <v>-13.59304552147358</v>
+        <v>-14.60823882451312</v>
       </c>
       <c r="F53">
-        <v>-1.238042948100174</v>
+        <v>-2.022267986278184</v>
       </c>
       <c r="G53">
-        <v>-8.120636936678984</v>
+        <v>-9.536984324199837</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.663304641488474</v>
       </c>
       <c r="E54">
-        <v>-13.07769159397867</v>
+        <v>-13.61979068896289</v>
       </c>
       <c r="F54">
-        <v>-1.025188121947366</v>
+        <v>-1.59034862307813</v>
       </c>
       <c r="G54">
-        <v>-8.477987153824534</v>
+        <v>-9.450244720525394</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.975025290229869</v>
       </c>
       <c r="E55">
-        <v>-12.60463361371541</v>
+        <v>-13.54441423910521</v>
       </c>
       <c r="F55">
-        <v>-1.505113570709179</v>
+        <v>-1.288804681954797</v>
       </c>
       <c r="G55">
-        <v>-8.509116213530302</v>
+        <v>-9.9989345382042</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.332318903627536</v>
       </c>
       <c r="E56">
-        <v>-12.18766984098515</v>
+        <v>-12.91844780549895</v>
       </c>
       <c r="F56">
-        <v>-1.597000187922976</v>
+        <v>-1.615044141270535</v>
       </c>
       <c r="G56">
-        <v>-8.519683474891655</v>
+        <v>-9.975694508518515</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.735926687760385</v>
       </c>
       <c r="E57">
-        <v>-11.90088158207939</v>
+        <v>-12.77125881482764</v>
       </c>
       <c r="F57">
-        <v>-1.478302221413747</v>
+        <v>-1.799302781561211</v>
       </c>
       <c r="G57">
-        <v>-8.379644088034945</v>
+        <v>-9.217251836017025</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.178616188937599</v>
       </c>
       <c r="E58">
-        <v>-12.27852008652703</v>
+        <v>-12.0569282679097</v>
       </c>
       <c r="F58">
-        <v>-1.634746234711559</v>
+        <v>-1.701524778341979</v>
       </c>
       <c r="G58">
-        <v>-8.767017642676144</v>
+        <v>-9.736590356944655</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.651439090401362</v>
       </c>
       <c r="E59">
-        <v>-11.73130381591415</v>
+        <v>-12.50200027880556</v>
       </c>
       <c r="F59">
-        <v>-1.456449455339555</v>
+        <v>-1.711205180750103</v>
       </c>
       <c r="G59">
-        <v>-7.740496924041092</v>
+        <v>-10.31260210695907</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.143653833787089</v>
       </c>
       <c r="E60">
-        <v>-11.21531137358416</v>
+        <v>-11.50766059857134</v>
       </c>
       <c r="F60">
-        <v>-1.756512631431952</v>
+        <v>-2.148214574762379</v>
       </c>
       <c r="G60">
-        <v>-8.152487695312313</v>
+        <v>-9.173506287261096</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.637692344872435</v>
       </c>
       <c r="E61">
-        <v>-11.76185743004391</v>
+        <v>-12.13973594361396</v>
       </c>
       <c r="F61">
-        <v>-1.845118601841916</v>
+        <v>-1.893534075382815</v>
       </c>
       <c r="G61">
-        <v>-8.336037582191665</v>
+        <v>-9.364107636139096</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.118445473510625</v>
       </c>
       <c r="E62">
-        <v>-11.39619673934655</v>
+        <v>-12.58636122109445</v>
       </c>
       <c r="F62">
-        <v>-1.676464215936065</v>
+        <v>-1.854775248661308</v>
       </c>
       <c r="G62">
-        <v>-8.048728577020475</v>
+        <v>-10.79253851487829</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.567235626982429</v>
       </c>
       <c r="E63">
-        <v>-10.28906182852928</v>
+        <v>-12.33176588390922</v>
       </c>
       <c r="F63">
-        <v>-1.845139190018817</v>
+        <v>-2.183665831679491</v>
       </c>
       <c r="G63">
-        <v>-8.984930992253132</v>
+        <v>-10.23182810634639</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.961585648242306</v>
       </c>
       <c r="E64">
-        <v>-10.51037741023214</v>
+        <v>-11.26138859661221</v>
       </c>
       <c r="F64">
-        <v>-1.781278624537594</v>
+        <v>-1.729559540457088</v>
       </c>
       <c r="G64">
-        <v>-8.947108009466959</v>
+        <v>-9.453419533697554</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.287307849448336</v>
       </c>
       <c r="E65">
-        <v>-10.97469543566061</v>
+        <v>-11.51182226618439</v>
       </c>
       <c r="F65">
-        <v>-1.887143822014017</v>
+        <v>-2.44151849400768</v>
       </c>
       <c r="G65">
-        <v>-8.929677987202695</v>
+        <v>-9.939712189052177</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.532500424222723</v>
       </c>
       <c r="E66">
-        <v>-10.37717234729652</v>
+        <v>-12.02401984729596</v>
       </c>
       <c r="F66">
-        <v>-2.09650024179962</v>
+        <v>-2.142372283640323</v>
       </c>
       <c r="G66">
-        <v>-8.615682674439441</v>
+        <v>-10.55087531160257</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.690877618461373</v>
       </c>
       <c r="E67">
-        <v>-10.09260756912852</v>
+        <v>-11.6075859060246</v>
       </c>
       <c r="F67">
-        <v>-2.273663087736169</v>
+        <v>-1.885468261155482</v>
       </c>
       <c r="G67">
-        <v>-8.260802124266188</v>
+        <v>-10.98450049797293</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.762945540988034</v>
       </c>
       <c r="E68">
-        <v>-9.625250937640908</v>
+        <v>-11.33862624928703</v>
       </c>
       <c r="F68">
-        <v>-1.905538566221846</v>
+        <v>-2.014862577417589</v>
       </c>
       <c r="G68">
-        <v>-9.178515142662015</v>
+        <v>-9.909817962832559</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.752790780737368</v>
       </c>
       <c r="E69">
-        <v>-9.620278673180486</v>
+        <v>-11.52867271796694</v>
       </c>
       <c r="F69">
-        <v>-1.801735353847326</v>
+        <v>-1.659956457326482</v>
       </c>
       <c r="G69">
-        <v>-8.072478430719206</v>
+        <v>-10.13600105516664</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.669530451818221</v>
       </c>
       <c r="E70">
-        <v>-9.655125280669509</v>
+        <v>-11.42731641272726</v>
       </c>
       <c r="F70">
-        <v>-1.96577323700967</v>
+        <v>-2.262853503010337</v>
       </c>
       <c r="G70">
-        <v>-8.642753005314061</v>
+        <v>-9.755480329791736</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.524879278016639</v>
       </c>
       <c r="E71">
-        <v>-10.06647374563025</v>
+        <v>-11.58793685730532</v>
       </c>
       <c r="F71">
-        <v>-2.045339414054306</v>
+        <v>-2.243022337537204</v>
       </c>
       <c r="G71">
-        <v>-9.270710525385178</v>
+        <v>-9.305593743732478</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.32907237264613</v>
       </c>
       <c r="E72">
-        <v>-10.5807861241034</v>
+        <v>-11.1138463849683</v>
       </c>
       <c r="F72">
-        <v>-2.023552371775605</v>
+        <v>-1.923109783353647</v>
       </c>
       <c r="G72">
-        <v>-9.109460473258357</v>
+        <v>-10.10159124483146</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.090518094519418</v>
       </c>
       <c r="E73">
-        <v>-10.78676829281629</v>
+        <v>-11.20526268976114</v>
       </c>
       <c r="F73">
-        <v>-2.098266073895334</v>
+        <v>-2.344005761529285</v>
       </c>
       <c r="G73">
-        <v>-8.999821826088773</v>
+        <v>-9.488557664051379</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.819650681204907</v>
       </c>
       <c r="E74">
-        <v>-11.28854585523621</v>
+        <v>-11.69203288931964</v>
       </c>
       <c r="F74">
-        <v>-2.472785599896201</v>
+        <v>-1.99308899663917</v>
       </c>
       <c r="G74">
-        <v>-8.926635595852105</v>
+        <v>-10.06080532378764</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.523947600701367</v>
       </c>
       <c r="E75">
-        <v>-11.01483130079059</v>
+        <v>-12.90238077971973</v>
       </c>
       <c r="F75">
-        <v>-2.285286697302537</v>
+        <v>-2.597021785991722</v>
       </c>
       <c r="G75">
-        <v>-8.228431609983193</v>
+        <v>-9.901839548082915</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.210314790696325</v>
       </c>
       <c r="E76">
-        <v>-11.85557872810665</v>
+        <v>-10.47023701662815</v>
       </c>
       <c r="F76">
-        <v>-2.333442443073304</v>
+        <v>-2.492360205011033</v>
       </c>
       <c r="G76">
-        <v>-8.801142746094952</v>
+        <v>-10.32199412465398</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.888574675091809</v>
       </c>
       <c r="E77">
-        <v>-10.9752796088076</v>
+        <v>-13.78944996766026</v>
       </c>
       <c r="F77">
-        <v>-2.654572867105834</v>
+        <v>-2.120871892132317</v>
       </c>
       <c r="G77">
-        <v>-8.537573662985876</v>
+        <v>-9.840428928329434</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.565065076491764</v>
       </c>
       <c r="E78">
-        <v>-12.54113987965386</v>
+        <v>-12.50801862076176</v>
       </c>
       <c r="F78">
-        <v>-2.538016070994279</v>
+        <v>-2.591314901725436</v>
       </c>
       <c r="G78">
-        <v>-8.926105908565821</v>
+        <v>-10.56067783694435</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.246777075004575</v>
       </c>
       <c r="E79">
-        <v>-12.2071241653221</v>
+        <v>-13.79108927525103</v>
       </c>
       <c r="F79">
-        <v>-2.822740263442687</v>
+        <v>-2.611107266403641</v>
       </c>
       <c r="G79">
-        <v>-7.986232098330114</v>
+        <v>-9.651330567126264</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.941737952084941</v>
       </c>
       <c r="E80">
-        <v>-13.00885426058808</v>
+        <v>-14.20053125265455</v>
       </c>
       <c r="F80">
-        <v>-2.892109749950766</v>
+        <v>-2.446903094120175</v>
       </c>
       <c r="G80">
-        <v>-8.84811938729721</v>
+        <v>-9.737093559866624</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.653364853009318</v>
       </c>
       <c r="E81">
-        <v>-13.10920524459805</v>
+        <v>-14.82872569547259</v>
       </c>
       <c r="F81">
-        <v>-2.968867224554369</v>
+        <v>-3.251398776162851</v>
       </c>
       <c r="G81">
-        <v>-9.047917431683306</v>
+        <v>-9.78666566877167</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.386841943043972</v>
       </c>
       <c r="E82">
-        <v>-13.75297763800248</v>
+        <v>-15.25294861203714</v>
       </c>
       <c r="F82">
-        <v>-2.827686177016604</v>
+        <v>-2.910873497636892</v>
       </c>
       <c r="G82">
-        <v>-8.707844951707212</v>
+        <v>-8.83013319338235</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.144442930983272</v>
       </c>
       <c r="E83">
-        <v>-15.23768765463129</v>
+        <v>-16.19759281851118</v>
       </c>
       <c r="F83">
-        <v>-3.06056854817606</v>
+        <v>-3.377031790875789</v>
       </c>
       <c r="G83">
-        <v>-8.214908031455272</v>
+        <v>-9.350646957976419</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.925232461555044</v>
       </c>
       <c r="E84">
-        <v>-15.29350109677583</v>
+        <v>-17.29715612078763</v>
       </c>
       <c r="F84">
-        <v>-3.421990826256242</v>
+        <v>-2.986937309049533</v>
       </c>
       <c r="G84">
-        <v>-8.289709807915104</v>
+        <v>-9.947482039432847</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.733389421628014</v>
       </c>
       <c r="E85">
-        <v>-15.91019321561438</v>
+        <v>-17.02936933881805</v>
       </c>
       <c r="F85">
-        <v>-3.133408726197824</v>
+        <v>-3.149699517096992</v>
       </c>
       <c r="G85">
-        <v>-7.80850877159988</v>
+        <v>-10.26005712815975</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.569326706047449</v>
       </c>
       <c r="E86">
-        <v>-18.69334805598851</v>
+        <v>-18.93530442221833</v>
       </c>
       <c r="F86">
-        <v>-3.504963554724988</v>
+        <v>-3.164311579725794</v>
       </c>
       <c r="G86">
-        <v>-7.960297284575463</v>
+        <v>-9.754242185760049</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.434843622366048</v>
       </c>
       <c r="E87">
-        <v>-19.4324493557284</v>
+        <v>-19.93452579743282</v>
       </c>
       <c r="F87">
-        <v>-3.450041425430506</v>
+        <v>-3.702735165739151</v>
       </c>
       <c r="G87">
-        <v>-8.096019720048965</v>
+        <v>-10.06415228532784</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.333718464236826</v>
       </c>
       <c r="E88">
-        <v>-20.72781934562251</v>
+        <v>-21.15973161105208</v>
       </c>
       <c r="F88">
-        <v>-3.543867290537758</v>
+        <v>-3.243326627111856</v>
       </c>
       <c r="G88">
-        <v>-8.036969519264984</v>
+        <v>-8.698413207465828</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.268154751784954</v>
       </c>
       <c r="E89">
-        <v>-21.12566842956639</v>
+        <v>-23.05910946408926</v>
       </c>
       <c r="F89">
-        <v>-3.729370723677969</v>
+        <v>-3.668812976883395</v>
       </c>
       <c r="G89">
-        <v>-8.080724999657532</v>
+        <v>-9.472571039642238</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.243315873823981</v>
       </c>
       <c r="E90">
-        <v>-22.90026418132221</v>
+        <v>-24.05276534474832</v>
       </c>
       <c r="F90">
-        <v>-3.562257283627841</v>
+        <v>-3.752768394872672</v>
       </c>
       <c r="G90">
-        <v>-7.819810974070951</v>
+        <v>-8.65511127181216</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.262948495529994</v>
       </c>
       <c r="E91">
-        <v>-25.11106519186688</v>
+        <v>-25.79022308116724</v>
       </c>
       <c r="F91">
-        <v>-3.950242269174732</v>
+        <v>-3.502347272552682</v>
       </c>
       <c r="G91">
-        <v>-8.546273776663082</v>
+        <v>-9.878328053663012</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.332436792993955</v>
       </c>
       <c r="E92">
-        <v>-26.77039316623146</v>
+        <v>-27.61895673968476</v>
       </c>
       <c r="F92">
-        <v>-3.562722101314022</v>
+        <v>-4.008449796390793</v>
       </c>
       <c r="G92">
-        <v>-8.445285584987614</v>
+        <v>-10.21526213646788</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.459219354209023</v>
       </c>
       <c r="E93">
-        <v>-29.75150571937688</v>
+        <v>-30.23734984600081</v>
       </c>
       <c r="F93">
-        <v>-3.765358856900415</v>
+        <v>-3.346576334268931</v>
       </c>
       <c r="G93">
-        <v>-9.070419209713732</v>
+        <v>-8.779690411000475</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.646697583607451</v>
       </c>
       <c r="E94">
-        <v>-30.90834289666534</v>
+        <v>-31.87106929985201</v>
       </c>
       <c r="F94">
-        <v>-3.502427249701412</v>
+        <v>-3.046806935623849</v>
       </c>
       <c r="G94">
-        <v>-8.849734933520375</v>
+        <v>-10.44324285502979</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.901909956008515</v>
       </c>
       <c r="E95">
-        <v>-32.76717505767484</v>
+        <v>-34.06336243712733</v>
       </c>
       <c r="F95">
-        <v>-3.764061009902712</v>
+        <v>-3.857307238644914</v>
       </c>
       <c r="G95">
-        <v>-9.289431660409756</v>
+        <v>-10.00635347075771</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.239264343678834</v>
       </c>
       <c r="E96">
-        <v>-35.42581497673407</v>
+        <v>-35.86071150653469</v>
       </c>
       <c r="F96">
-        <v>-3.364883182798454</v>
+        <v>-3.508154722144599</v>
       </c>
       <c r="G96">
-        <v>-10.00164587500086</v>
+        <v>-9.836284125314267</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.654761595370517</v>
       </c>
       <c r="E97">
-        <v>-38.18505041739967</v>
+        <v>-40.04354747133261</v>
       </c>
       <c r="F97">
-        <v>-3.496565162255413</v>
+        <v>-3.235958435340275</v>
       </c>
       <c r="G97">
-        <v>-9.816851222998745</v>
+        <v>-10.89422854220808</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.175410193403208</v>
       </c>
       <c r="E98">
-        <v>-40.85428922987385</v>
+        <v>-41.01423266758776</v>
       </c>
       <c r="F98">
-        <v>-3.491782370390785</v>
+        <v>-3.545654502663332</v>
       </c>
       <c r="G98">
-        <v>-9.881108911915998</v>
+        <v>-10.42408803853956</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.770386136351644</v>
       </c>
       <c r="E99">
-        <v>-42.76736571678423</v>
+        <v>-44.25652043065157</v>
       </c>
       <c r="F99">
-        <v>-3.326338948228488</v>
+        <v>-3.28945918857565</v>
       </c>
       <c r="G99">
-        <v>-10.71621388747039</v>
+        <v>-11.15654292855777</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.481199396213854</v>
       </c>
       <c r="E100">
-        <v>-46.26815462586489</v>
+        <v>-47.44403177211859</v>
       </c>
       <c r="F100">
-        <v>-3.457355771200963</v>
+        <v>-2.998661483941532</v>
       </c>
       <c r="G100">
-        <v>-11.01814557228854</v>
+        <v>-11.28138691138923</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.217894538664872</v>
       </c>
       <c r="E101">
-        <v>-48.36577095706184</v>
+        <v>-49.67885067668144</v>
       </c>
       <c r="F101">
-        <v>-3.488151724579641</v>
+        <v>-3.155409568775108</v>
       </c>
       <c r="G101">
-        <v>-11.73823226417204</v>
+        <v>-11.78794672653527</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.082317993963237</v>
       </c>
       <c r="E102">
-        <v>-51.10664909621886</v>
+        <v>-51.21475848832247</v>
       </c>
       <c r="F102">
-        <v>-3.083568709185987</v>
+        <v>-3.174102049695041</v>
       </c>
       <c r="G102">
-        <v>-12.33157803063007</v>
+        <v>-12.23229476990733</v>
       </c>
     </row>
   </sheetData>
